--- a/src/test/resources/ImportTemplate/Pushdown.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B694DA9-91BC-4D7B-A657-D4189BB148BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBF3400-F5C5-4F09-89BF-02A79A130075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,10 +33,10 @@
     <t>sourceSql</t>
   </si>
   <si>
-    <t>SELECT * FROM public.STAFF</t>
+    <t>Pushdown_ImportSQL-DB-PostgreSQL--Customer</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQL-DB--STAFF--</t>
+    <t>SELECT * FROM public.Customer</t>
   </si>
 </sst>
 </file>
@@ -367,7 +367,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -380,10 +380,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ImportTemplate/Pushdown.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACBF3400-F5C5-4F09-89BF-02A79A130075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504458C3-78CF-4907-B0A8-ABB67D53ACB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,10 +33,10 @@
     <t>sourceSql</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQL-DB-PostgreSQL--Customer</t>
+    <t>SELECT * FROM public.Customer</t>
   </si>
   <si>
-    <t>SELECT * FROM public.Customer</t>
+    <t>Pushdown_ImportSQL DB PostgreSQL Customer</t>
   </si>
 </sst>
 </file>
@@ -380,10 +380,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ImportTemplate/Pushdown.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504458C3-78CF-4907-B0A8-ABB67D53ACB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FFB963-7157-475D-9A2E-042C80617E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,10 +33,10 @@
     <t>sourceSql</t>
   </si>
   <si>
-    <t>SELECT * FROM public.Customer</t>
+    <t>Pushdown_ImportSQL DB PostgreSQL Customer</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQL DB PostgreSQL Customer</t>
+    <t>SELECT * FROM public.customer</t>
   </si>
 </sst>
 </file>
@@ -380,10 +380,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ImportTemplate/Pushdown.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FFB963-7157-475D-9A2E-042C80617E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC4F5FA-D26E-42AB-B57A-0EDB934E5E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,10 @@
     <t>sourceSql</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQL DB PostgreSQL Customer</t>
+    <t>SELECT * FROM public.customer</t>
   </si>
   <si>
-    <t>SELECT * FROM public.customer</t>
+    <t>Pushdown_ImportSQ-- DB-PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>
@@ -380,10 +380,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ImportTemplate/Pushdown.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC4F5FA-D26E-42AB-B57A-0EDB934E5E9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EBA8F4-6FD2-41CC-AF58-68D7573FB300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
     <t>SELECT * FROM public.customer</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQ-- DB-PostgreSQL_Customer</t>
+    <t>Pushdown_ImportSQ__DB_PostgreSQL_Customer</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/ImportTemplate/Pushdown.xlsx
+++ b/src/test/resources/ImportTemplate/Pushdown.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Eclipse\ICEDQ\TestGenerator\src\test\resources\ImportTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96EBA8F4-6FD2-41CC-AF58-68D7573FB300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD6EF39-4D57-4980-A400-FDBDB952A0FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,10 +33,10 @@
     <t>sourceSql</t>
   </si>
   <si>
-    <t>SELECT * FROM public.customer</t>
+    <t>Pushdown_ImportSQ__DB_PostgreSQL_Customer</t>
   </si>
   <si>
-    <t>Pushdown_ImportSQ__DB_PostgreSQL_Customer</t>
+    <t>SELECT * FROM icedq.customer</t>
   </si>
 </sst>
 </file>
@@ -380,10 +380,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
